--- a/SAMPLE.xlsx
+++ b/SAMPLE.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kcassidy\Documents\GitHub\quiz_processing_system_v6_personal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kcassidy\Documents\GitHub\quiz_processing_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F4492E-1EBF-4D88-B96F-8A6780F4D5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8DC237-4E23-4BBD-9257-52E3D17C50C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58413554-941A-47F6-8893-9DE0674C0595}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58413554-941A-47F6-8893-9DE0674C0595}"/>
   </bookViews>
   <sheets>
-    <sheet name="SAMPLE - Grade 8 Math" sheetId="1" r:id="rId1"/>
+    <sheet name="SAMPLE ROSTER" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -205,6 +205,12 @@
       </rPr>
       <t>- If students get added to your class, add them alphabetically where they belong, then refresh the rosters on the Quiz Processing System before running a new PDF.</t>
     </r>
+  </si>
+  <si>
+    <t>blank</t>
+  </si>
+  <si>
+    <t>Want to practice before using your own roster and file? Try adding this class to the Quiz Processing System, and use the file called "Sample_Quiz.pdf"</t>
   </si>
 </sst>
 </file>
@@ -269,12 +275,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -621,7 +625,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -629,6 +633,12 @@
       </c>
       <c r="C1" t="s">
         <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -702,7 +712,7 @@
       <c r="C7">
         <v>11116</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>43</v>
       </c>
     </row>
@@ -716,7 +726,7 @@
       <c r="C8">
         <v>11117</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -741,7 +751,7 @@
       <c r="C10">
         <v>11119</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -755,7 +765,7 @@
       <c r="C11">
         <v>11120</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" t="s">
         <v>40</v>
       </c>
     </row>
@@ -769,7 +779,7 @@
       <c r="C12">
         <v>11121</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" t="s">
         <v>44</v>
       </c>
     </row>
@@ -868,6 +878,9 @@
       </c>
       <c r="C20">
         <v>11129</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
